--- a/assets/templates/excel/sales-report.xlsx
+++ b/assets/templates/excel/sales-report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售报表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,7 +27,25 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002B579A"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002B579A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,8 +57,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="002B579A"/>
+        <bgColor rgb="002B579A"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,10 +74,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,71 +455,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>金额</t>
+          <t>SALES REPORT / 销售报表</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>示例数据</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Period:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>示例数据</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>示例数据</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>示例数据</t>
+          <t>{{report_period}}</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Date:</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>示例数据</t>
+          <t>{{report_date}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>SUMMARY / 汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>vs Last Period</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Total Sales / 总销售额</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>{{total_sales}}</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>{{sales_change}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Total Units / 总销量</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>{{total_units}}</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>{{units_change}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Average Price / 均价</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>{{avg_price}}</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>{{price_change}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Growth Rate / 增长率</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>{{growth_rate}}</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCTS / 产品明细</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>{{product_name}}</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{{category}}</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>{{units_sold}}</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{{unit_price}}</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>{{revenue}}</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>{{market_share}}</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>